--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486747_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486747_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. ESTEBANEZ ESCUDERO</t>
+          <t>P. PEREZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.0568</v>
+        <v>-0.5352</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.0076</v>
+        <v>-0.6251</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0492</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.6151</v>
+        <v>-0.4555</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.952</v>
+        <v>2.9039</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3369</v>
+        <v>-3.3593</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.1522</v>
+        <v>2.1181</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0828</v>
+        <v>4.1459</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.235</v>
+        <v>-2.0277</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.4629</v>
+        <v>-2.5736</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.0348</v>
+        <v>-1.242</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5719</v>
+        <v>-1.3316</v>
       </c>
       <c r="P2" t="n">
-        <v>1.7377</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-2.8962</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7377</v>
+        <v>2.8962</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3805</v>
+        <v>-0.8138</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8554</v>
+        <v>-0.7038</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4749</v>
+        <v>-0.1099</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.7989</v>
+        <v>0.7341</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>0.8568</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.7989</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. PEREZ FERNANDEZ</t>
+          <t>M. ESTEBANEZ ESCUDERO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.1061</v>
+        <v>-0.966</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.2456</v>
+        <v>-0.5939</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1395</v>
+        <v>-0.372</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.4555</v>
+        <v>-0.6151</v>
       </c>
       <c r="H3" t="n">
-        <v>2.9039</v>
+        <v>-0.952</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.3593</v>
+        <v>0.3369</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1181</v>
+        <v>-0.1522</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1459</v>
+        <v>0.0828</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.0277</v>
+        <v>-0.235</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.5736</v>
+        <v>-0.4629</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.242</v>
+        <v>-1.0348</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.3316</v>
+        <v>0.5719</v>
       </c>
       <c r="P3" t="n">
+        <v>1.7377</v>
+      </c>
+      <c r="Q3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-2.8962</v>
-      </c>
       <c r="R3" t="n">
-        <v>2.8962</v>
+        <v>1.7377</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3847</v>
+        <v>-0.2896</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3244</v>
+        <v>-0.4417</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0603</v>
+        <v>0.152</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7341</v>
+        <v>-1.7989</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8568</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1228</v>
+        <v>-1.7989</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.3636</v>
+        <v>-1.8559</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.4082</v>
+        <v>-2.9253</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0446</v>
+        <v>1.0694</v>
       </c>
       <c r="G4" t="n">
         <v>-2.3398</v>
@@ -766,13 +766,13 @@
         <v>1.5446</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7059</v>
+        <v>0.2136</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6339</v>
+        <v>0.1168</v>
       </c>
       <c r="U4" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0968</v>
       </c>
       <c r="V4" t="n">
         <v>0.6565</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. CORREA BOULATOVA</t>
+          <t>D. GARCIA CASARRUBIOS CASTRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.0901</v>
+        <v>-2.8653</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0544</v>
+        <v>-4.8311</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.1445</v>
+        <v>1.9658</v>
       </c>
       <c r="G5" t="n">
-        <v>-4.1792</v>
+        <v>-3.3246</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5304</v>
+        <v>-3.5709</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.6488</v>
+        <v>0.2463</v>
       </c>
       <c r="J5" t="n">
-        <v>1.263</v>
+        <v>-2.5235</v>
       </c>
       <c r="K5" t="n">
-        <v>1.263</v>
+        <v>-2.6049</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.0814</v>
       </c>
       <c r="M5" t="n">
-        <v>-5.4422</v>
+        <v>-0.8011</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.7934</v>
+        <v>-0.9661</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.6488</v>
+        <v>0.165</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9654</v>
+        <v>0.5792</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9308</v>
+        <v>2.51</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4118</v>
+        <v>-1.062</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1855</v>
+        <v>-0.6624</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2263</v>
+        <v>-0.3996</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2882</v>
+        <v>0.9421</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5712</v>
+        <v>0.2856</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.8594000000000001</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. GARCIA CASARRUBIOS CASTRO</t>
+          <t>I. CORREA BOULATOVA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.5025</v>
+        <v>-3.0195</v>
       </c>
       <c r="E6" t="n">
-        <v>-5.2448</v>
+        <v>1.0753</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7423</v>
+        <v>-4.0948</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.3246</v>
+        <v>-4.1792</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.5709</v>
+        <v>-0.5304</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2463</v>
+        <v>-3.6488</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.5235</v>
+        <v>1.263</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.6049</v>
+        <v>1.263</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0814</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8011</v>
+        <v>-5.4422</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9661</v>
+        <v>-1.7934</v>
       </c>
       <c r="O6" t="n">
-        <v>0.165</v>
+        <v>-3.6488</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5792</v>
+        <v>0.9654</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R6" t="n">
-        <v>2.51</v>
+        <v>1.9308</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.6992</v>
+        <v>0.4825</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0761</v>
+        <v>0.2065</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6231</v>
+        <v>0.276</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9421</v>
+        <v>-0.2882</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2856</v>
+        <v>0.5712</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6565</v>
+        <v>-0.8594000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.8465</v>
+        <v>-3.3583</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1847</v>
+        <v>-0.771</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.6618</v>
+        <v>-2.5873</v>
       </c>
       <c r="G7" t="n">
         <v>-5.9441</v>
@@ -1000,13 +1000,13 @@
         <v>2.3169</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9157999999999999</v>
+        <v>-0.4277</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8829</v>
+        <v>-0.4692</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0329</v>
+        <v>0.0416</v>
       </c>
       <c r="V7" t="n">
         <v>0.6965</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.0101</v>
+        <v>-3.9508</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6245</v>
+        <v>-1.4659</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.3856</v>
+        <v>-2.4849</v>
       </c>
       <c r="G8" t="n">
         <v>-0.7936</v>
@@ -1078,13 +1078,13 @@
         <v>1.5446</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8661</v>
+        <v>-0.8068</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6622</v>
+        <v>-0.5036</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2039</v>
+        <v>-0.3032</v>
       </c>
       <c r="V8" t="n">
         <v>-1.9643</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.1445</v>
+        <v>-4.5085</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.4151</v>
+        <v>-3.8288</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7294</v>
+        <v>-0.6797</v>
       </c>
       <c r="G9" t="n">
         <v>-4.5495</v>
@@ -1156,13 +1156,13 @@
         <v>1.9308</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6673</v>
+        <v>0.3033</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5236</v>
+        <v>0.1099</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1437</v>
+        <v>0.1934</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2277</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.9398</v>
+        <v>-5.5507</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0626</v>
+        <v>-0.5246</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.8772</v>
+        <v>-5.0262</v>
       </c>
       <c r="G10" t="n">
         <v>-5.7242</v>
@@ -1234,13 +1234,13 @@
         <v>2.7031</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5625</v>
+        <v>-0.0484</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2753</v>
+        <v>-0.1866</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2872</v>
+        <v>0.1382</v>
       </c>
       <c r="V10" t="n">
         <v>-1.5158</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.9461</v>
+        <v>-7.5061</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.748</v>
+        <v>-5.3826</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1981</v>
+        <v>-2.1236</v>
       </c>
       <c r="G11" t="n">
         <v>-4.9215</v>
@@ -1312,13 +1312,13 @@
         <v>1.5446</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5849</v>
+        <v>-0.1449</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6347</v>
+        <v>-0.2692</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0498</v>
+        <v>0.1243</v>
       </c>
       <c r="V11" t="n">
         <v>-0.1228</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.016500000000001</v>
+        <v>-7.6303</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7135</v>
+        <v>-2.4515</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.303</v>
+        <v>-5.1788</v>
       </c>
       <c r="G12" t="n">
         <v>-4.6346</v>
@@ -1390,13 +1390,13 @@
         <v>1.5446</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9656</v>
+        <v>-0.5794</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7725</v>
+        <v>-0.5105</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.193</v>
+        <v>-0.0689</v>
       </c>
       <c r="V12" t="n">
         <v>-1.0648</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-42.0226</v>
+        <v>-41.74659999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-22.6002</v>
+        <v>-22.3245</v>
       </c>
       <c r="F13" t="n">
-        <v>-19.4224</v>
+        <v>-19.4222</v>
       </c>
       <c r="G13" t="n">
         <v>-37.4817</v>
@@ -1441,10 +1441,10 @@
         <v>-25.0711</v>
       </c>
       <c r="J13" t="n">
-        <v>-6.265100000000001</v>
+        <v>-6.2651</v>
       </c>
       <c r="K13" t="n">
-        <v>1.3869</v>
+        <v>1.386899999999999</v>
       </c>
       <c r="L13" t="n">
         <v>-7.652</v>
@@ -1468,10 +1468,10 @@
         <v>22.2039</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.4493</v>
+        <v>-3.1732</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.5899</v>
+        <v>-3.3138</v>
       </c>
       <c r="U13" t="n">
         <v>0.1406999999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.0528</v>
+        <v>8.5243</v>
       </c>
       <c r="E14" t="n">
-        <v>4.342</v>
+        <v>4.9626</v>
       </c>
       <c r="F14" t="n">
-        <v>3.7108</v>
+        <v>3.5618</v>
       </c>
       <c r="G14" t="n">
         <v>9.7791</v>
@@ -1546,13 +1546,13 @@
         <v>1.3515</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7837</v>
+        <v>1.2552</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5518</v>
+        <v>0.0687</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3355</v>
+        <v>1.1865</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.8338</v>
+        <v>8.1648</v>
       </c>
       <c r="E15" t="n">
-        <v>6.3454</v>
+        <v>6.5523</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4884</v>
+        <v>1.6126</v>
       </c>
       <c r="G15" t="n">
         <v>5.7686</v>
@@ -1624,13 +1624,13 @@
         <v>1.5446</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9379999999999999</v>
+        <v>1.269</v>
       </c>
       <c r="T15" t="n">
-        <v>0.248</v>
+        <v>0.4549</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8142</v>
       </c>
       <c r="V15" t="n">
         <v>1.5133</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.8118</v>
+        <v>7.1872</v>
       </c>
       <c r="E16" t="n">
-        <v>5.4086</v>
+        <v>4.6847</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4032</v>
+        <v>2.5025</v>
       </c>
       <c r="G16" t="n">
         <v>5.9099</v>
@@ -1702,13 +1702,13 @@
         <v>1.9308</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3074</v>
+        <v>0.6828</v>
       </c>
       <c r="T16" t="n">
-        <v>0.772</v>
+        <v>0.048</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5354</v>
+        <v>0.6348</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3709</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>J. SCHILB</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.1212</v>
+        <v>4.4643</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6783</v>
+        <v>3.7918</v>
       </c>
       <c r="F17" t="n">
-        <v>3.4429</v>
+        <v>0.6725</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3259</v>
+        <v>4.3606</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6206</v>
+        <v>0.6825</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7053</v>
+        <v>3.6781</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9751</v>
+        <v>5.0438</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6903</v>
+        <v>1.0967</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2848</v>
+        <v>3.9471</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3508</v>
+        <v>-0.6832</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0697</v>
+        <v>-0.4142</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4205</v>
+        <v>-0.269</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1931</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.9308</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1239</v>
+        <v>1.5446</v>
       </c>
       <c r="S17" t="n">
-        <v>2.2893</v>
+        <v>-0.124</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4063</v>
+        <v>-0.2207</v>
       </c>
       <c r="U17" t="n">
-        <v>0.883</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>1.3129</v>
+        <v>0.6138</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2277</v>
+        <v>0.8995</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0852</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. SCHILB</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.4395</v>
+        <v>4.2938</v>
       </c>
       <c r="E18" t="n">
-        <v>3.7918</v>
+        <v>0.8509</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6477000000000001</v>
+        <v>3.4429</v>
       </c>
       <c r="G18" t="n">
-        <v>4.3606</v>
+        <v>1.3259</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6825</v>
+        <v>0.6206</v>
       </c>
       <c r="I18" t="n">
-        <v>3.6781</v>
+        <v>0.7053</v>
       </c>
       <c r="J18" t="n">
-        <v>5.0438</v>
+        <v>0.9751</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0967</v>
+        <v>0.6903</v>
       </c>
       <c r="L18" t="n">
-        <v>3.9471</v>
+        <v>0.2848</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6832</v>
+        <v>0.3508</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4142</v>
+        <v>-0.0697</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.269</v>
+        <v>0.4205</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3862</v>
+        <v>0.1931</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.9308</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5446</v>
+        <v>2.1239</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1489</v>
+        <v>1.4619</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2207</v>
+        <v>0.5789</v>
       </c>
       <c r="U18" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.883</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6138</v>
+        <v>1.3129</v>
       </c>
       <c r="W18" t="n">
-        <v>0.8995</v>
+        <v>1.2277</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2856</v>
+        <v>0.0852</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>4.1123</v>
+        <v>4.1427</v>
       </c>
       <c r="E19" t="n">
-        <v>2.9989</v>
+        <v>2.7921</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1134</v>
+        <v>1.3507</v>
       </c>
       <c r="G19" t="n">
         <v>1.8115</v>
@@ -1936,13 +1936,13 @@
         <v>2.1239</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3476</v>
+        <v>-0.3172</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1383</v>
+        <v>-0.3451</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2093</v>
+        <v>0.0279</v>
       </c>
       <c r="V19" t="n">
         <v>2.4554</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3.0311</v>
+        <v>3.5082</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5324</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>2.4988</v>
+        <v>2.5622</v>
       </c>
       <c r="G20" t="n">
         <v>2.1109</v>
@@ -2014,13 +2014,13 @@
         <v>0.9654</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0219</v>
+        <v>0.4552</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3863</v>
+        <v>0.0274</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3644</v>
+        <v>0.4278</v>
       </c>
       <c r="V20" t="n">
         <v>0.9421</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.5421</v>
+        <v>2.2219</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0299</v>
+        <v>0.547</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5122</v>
+        <v>1.6749</v>
       </c>
       <c r="G21" t="n">
         <v>2.9185</v>
@@ -2092,13 +2092,13 @@
         <v>1.5446</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.728</v>
+        <v>-0.0482</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.607</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.121</v>
+        <v>0.0417</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2277</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.3796</v>
+        <v>0.8376</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3891</v>
+        <v>-1.9062</v>
       </c>
       <c r="F22" t="n">
-        <v>2.7687</v>
+        <v>2.7438</v>
       </c>
       <c r="G22" t="n">
         <v>-0.2589</v>
@@ -2170,13 +2170,13 @@
         <v>1.5446</v>
       </c>
       <c r="S22" t="n">
-        <v>1.0592</v>
+        <v>0.5173</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6616</v>
+        <v>0.1445</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3976</v>
+        <v>0.3728</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2896</v>
+        <v>0.5599</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5368</v>
+        <v>-1.33</v>
       </c>
       <c r="F23" t="n">
-        <v>1.8264</v>
+        <v>1.8898</v>
       </c>
       <c r="G23" t="n">
         <v>4.2281</v>
@@ -2248,13 +2248,13 @@
         <v>1.5446</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6562</v>
+        <v>-0.3859</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.607</v>
+        <v>-0.4002</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0492</v>
+        <v>0.0142</v>
       </c>
       <c r="V23" t="n">
         <v>-0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.5912</v>
+        <v>-1.1927</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.7791</v>
+        <v>-2.4688</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1878</v>
+        <v>1.276</v>
       </c>
       <c r="G24" t="n">
         <v>-0.4728</v>
@@ -2326,13 +2326,13 @@
         <v>2.1239</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0259</v>
+        <v>-0.6274</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7174</v>
+        <v>-0.4071</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3085</v>
+        <v>-0.2203</v>
       </c>
       <c r="V24" t="n">
         <v>-0.2856</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>42.0226</v>
+        <v>42.712</v>
       </c>
       <c r="E25" t="n">
-        <v>19.4223</v>
+        <v>19.4225</v>
       </c>
       <c r="F25" t="n">
-        <v>22.6003</v>
+        <v>23.2897</v>
       </c>
       <c r="G25" t="n">
         <v>37.4814</v>
@@ -2404,13 +2404,13 @@
         <v>18.3424</v>
       </c>
       <c r="S25" t="n">
-        <v>3.449099999999999</v>
+        <v>4.1387</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1405999999999998</v>
+        <v>-0.1406000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>3.5898</v>
+        <v>4.2793</v>
       </c>
       <c r="V25" t="n">
         <v>4.9533</v>
